--- a/paper/route_length_analysis.xlsx
+++ b/paper/route_length_analysis.xlsx
@@ -408,13 +408,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>1545.62114371234</v>
+        <v>1663.098610497467</v>
       </c>
       <c r="C2">
-        <v>759.8502715122606</v>
+        <v>278.893922063128</v>
       </c>
       <c r="D2">
-        <v>785.770872200079</v>
+        <v>1384.204688434338</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -422,13 +422,13 @@
         <v>0.1</v>
       </c>
       <c r="B3">
-        <v>1545.62114371234</v>
+        <v>1663.098610497467</v>
       </c>
       <c r="C3">
-        <v>759.8502715122606</v>
+        <v>278.893922063128</v>
       </c>
       <c r="D3">
-        <v>785.770872200079</v>
+        <v>1384.204688434338</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -436,13 +436,13 @@
         <v>0.2</v>
       </c>
       <c r="B4">
-        <v>1545.62114371234</v>
+        <v>1542.49232650778</v>
       </c>
       <c r="C4">
-        <v>759.8502715122606</v>
+        <v>300.7249630787018</v>
       </c>
       <c r="D4">
-        <v>785.770872200079</v>
+        <v>1241.767363429078</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -450,13 +450,13 @@
         <v>0.3</v>
       </c>
       <c r="B5">
-        <v>1545.62114371234</v>
+        <v>1401.191101064397</v>
       </c>
       <c r="C5">
-        <v>759.8502715122606</v>
+        <v>332.2534352635386</v>
       </c>
       <c r="D5">
-        <v>785.770872200079</v>
+        <v>1068.937665800858</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -464,13 +464,13 @@
         <v>0.4</v>
       </c>
       <c r="B6">
-        <v>1407.789159054982</v>
+        <v>1401.191101064397</v>
       </c>
       <c r="C6">
-        <v>801.2061669984872</v>
+        <v>332.2534352635386</v>
       </c>
       <c r="D6">
-        <v>606.5829920564945</v>
+        <v>1068.937665800858</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -478,13 +478,13 @@
         <v>0.5</v>
       </c>
       <c r="B7">
-        <v>1407.789159054982</v>
+        <v>1401.191101064397</v>
       </c>
       <c r="C7">
-        <v>801.2061669984872</v>
+        <v>332.2534352635386</v>
       </c>
       <c r="D7">
-        <v>606.5829920564945</v>
+        <v>1068.937665800858</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -492,13 +492,13 @@
         <v>0.6000000000000001</v>
       </c>
       <c r="B8">
-        <v>1407.789159054982</v>
+        <v>1401.191101064397</v>
       </c>
       <c r="C8">
-        <v>801.2061669984872</v>
+        <v>332.2534352635386</v>
       </c>
       <c r="D8">
-        <v>606.5829920564945</v>
+        <v>1068.937665800858</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -506,13 +506,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B9">
-        <v>1407.789159054982</v>
+        <v>1401.191101064397</v>
       </c>
       <c r="C9">
-        <v>801.2061669984872</v>
+        <v>332.2534352635386</v>
       </c>
       <c r="D9">
-        <v>606.5829920564945</v>
+        <v>1068.937665800858</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -520,13 +520,13 @@
         <v>0.8</v>
       </c>
       <c r="B10">
-        <v>1380.136803310334</v>
+        <v>1401.191101064397</v>
       </c>
       <c r="C10">
-        <v>822.1442090163847</v>
+        <v>332.2534352635386</v>
       </c>
       <c r="D10">
-        <v>557.9925942939493</v>
+        <v>1068.937665800858</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -534,13 +534,13 @@
         <v>0.9</v>
       </c>
       <c r="B11">
-        <v>1380.136803310334</v>
+        <v>1401.191101064397</v>
       </c>
       <c r="C11">
-        <v>822.1442090163847</v>
+        <v>332.2534352635386</v>
       </c>
       <c r="D11">
-        <v>557.9925942939493</v>
+        <v>1068.937665800858</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -548,13 +548,13 @@
         <v>1</v>
       </c>
       <c r="B12">
-        <v>1380.136803310334</v>
+        <v>1401.191101064397</v>
       </c>
       <c r="C12">
-        <v>822.1442090163847</v>
+        <v>332.2534352635386</v>
       </c>
       <c r="D12">
-        <v>557.9925942939493</v>
+        <v>1068.937665800858</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -562,13 +562,13 @@
         <v>4</v>
       </c>
       <c r="B13">
-        <v>1362.1711469327</v>
+        <v>1366.663743633512</v>
       </c>
       <c r="C13">
-        <v>930.8574551055771</v>
+        <v>613.7855289495036</v>
       </c>
       <c r="D13">
-        <v>431.3136918271232</v>
+        <v>752.8782146840085</v>
       </c>
     </row>
   </sheetData>
